--- a/BVSimulationFiles/58.xlsx
+++ b/BVSimulationFiles/58.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.005343811394891945</v>
+        <v>0.01068762278978389</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005403784510391893</v>
+        <v>0.01080756902078379</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005463757625891841</v>
+        <v>0.01092751525178368</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00552373074139179</v>
+        <v>0.01104746148278358</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005583703856891737</v>
+        <v>0.01116740771378347</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005643676972391686</v>
+        <v>0.01128735394478337</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005703650087891634</v>
+        <v>0.01140730017578327</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005763623203391584</v>
+        <v>0.01152724640678317</v>
       </c>
       <c r="J2" t="n">
-        <v>0.005823596318891532</v>
+        <v>0.01164719263778306</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005883569434391479</v>
+        <v>0.01176713886878296</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005943542549891427</v>
+        <v>0.01188708509978285</v>
       </c>
       <c r="M2" t="n">
-        <v>0.006003515665391376</v>
+        <v>0.01200703133078275</v>
       </c>
       <c r="N2" t="n">
-        <v>0.006063488780891325</v>
+        <v>0.01212697756178265</v>
       </c>
       <c r="O2" t="n">
-        <v>0.006123461896391274</v>
+        <v>0.01224692379278255</v>
       </c>
       <c r="P2" t="n">
-        <v>0.006183435011891221</v>
+        <v>0.01236687002378244</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.006243408127391169</v>
+        <v>0.01248681625478234</v>
       </c>
       <c r="R2" t="n">
-        <v>0.006303381242891117</v>
+        <v>0.01260676248578223</v>
       </c>
       <c r="S2" t="n">
-        <v>0.006363354358391067</v>
+        <v>0.01272670871678213</v>
       </c>
       <c r="T2" t="n">
-        <v>0.006423327473891014</v>
+        <v>0.01284665494778203</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006483300589390963</v>
+        <v>0.01296660117878193</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.005343811394891945</v>
+        <v>0.01068762278978389</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005403784510391893</v>
+        <v>0.01080756902078379</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005463757625891841</v>
+        <v>0.01092751525178368</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00552373074139179</v>
+        <v>0.01104746148278358</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005583703856891737</v>
+        <v>0.01116740771378347</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005643676972391686</v>
+        <v>0.01128735394478337</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005703650087891634</v>
+        <v>0.01140730017578327</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005763623203391584</v>
+        <v>0.01152724640678317</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005823596318891532</v>
+        <v>0.01164719263778306</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005883569434391479</v>
+        <v>0.01176713886878296</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005943542549891427</v>
+        <v>0.01188708509978285</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006003515665391376</v>
+        <v>0.01200703133078275</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006063488780891325</v>
+        <v>0.01212697756178265</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006123461896391274</v>
+        <v>0.01224692379278255</v>
       </c>
       <c r="P3" t="n">
-        <v>0.006183435011891221</v>
+        <v>0.01236687002378244</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006243408127391169</v>
+        <v>0.01248681625478234</v>
       </c>
       <c r="R3" t="n">
-        <v>0.006303381242891117</v>
+        <v>0.01260676248578223</v>
       </c>
       <c r="S3" t="n">
-        <v>0.006363354358391067</v>
+        <v>0.01272670871678213</v>
       </c>
       <c r="T3" t="n">
-        <v>0.006423327473891014</v>
+        <v>0.01284665494778203</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006483300589390963</v>
+        <v>0.01296660117878193</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/58.xlsx
+++ b/BVSimulationFiles/58.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01068762278978389</v>
+        <v>0.1068762278978389</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01080756902078379</v>
+        <v>0.1080756902078379</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01092751525178368</v>
+        <v>0.1092751525178368</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01104746148278358</v>
+        <v>0.1104746148278358</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01116740771378347</v>
+        <v>0.1116740771378347</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01128735394478337</v>
+        <v>0.1128735394478337</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01140730017578327</v>
+        <v>0.1140730017578327</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01152724640678317</v>
+        <v>0.1152724640678317</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01164719263778306</v>
+        <v>0.1164719263778306</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01176713886878296</v>
+        <v>0.1176713886878296</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01188708509978285</v>
+        <v>0.1188708509978285</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01200703133078275</v>
+        <v>0.1200703133078275</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01212697756178265</v>
+        <v>0.1212697756178265</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01224692379278255</v>
+        <v>0.1224692379278255</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01236687002378244</v>
+        <v>0.1236687002378244</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01248681625478234</v>
+        <v>0.1248681625478234</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01260676248578223</v>
+        <v>0.1260676248578223</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01272670871678213</v>
+        <v>0.1272670871678213</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01284665494778203</v>
+        <v>0.1284665494778203</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01296660117878193</v>
+        <v>0.1296660117878193</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01068762278978389</v>
+        <v>0.1068762278978389</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01080756902078379</v>
+        <v>0.1080756902078379</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01092751525178368</v>
+        <v>0.1092751525178368</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01104746148278358</v>
+        <v>0.1104746148278358</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01116740771378347</v>
+        <v>0.1116740771378347</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01128735394478337</v>
+        <v>0.1128735394478337</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01140730017578327</v>
+        <v>0.1140730017578327</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01152724640678317</v>
+        <v>0.1152724640678317</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01164719263778306</v>
+        <v>0.1164719263778306</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01176713886878296</v>
+        <v>0.1176713886878296</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01188708509978285</v>
+        <v>0.1188708509978285</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01200703133078275</v>
+        <v>0.1200703133078275</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01212697756178265</v>
+        <v>0.1212697756178265</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01224692379278255</v>
+        <v>0.1224692379278255</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01236687002378244</v>
+        <v>0.1236687002378244</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01248681625478234</v>
+        <v>0.1248681625478234</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01260676248578223</v>
+        <v>0.1260676248578223</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01272670871678213</v>
+        <v>0.1272670871678213</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01284665494778203</v>
+        <v>0.1284665494778203</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01296660117878193</v>
+        <v>0.1296660117878193</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/58.xlsx
+++ b/BVSimulationFiles/58.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1068762278978389</v>
+        <v>0.3341823176612375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1080756902078379</v>
+        <v>0.3379328158083644</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1092751525178368</v>
+        <v>0.3416833139554912</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1104746148278358</v>
+        <v>0.3454338121026181</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1116740771378347</v>
+        <v>0.349184310249745</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1128735394478337</v>
+        <v>0.3529348083968719</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1140730017578327</v>
+        <v>0.3566853065439988</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1152724640678317</v>
+        <v>0.3604358046911257</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1164719263778306</v>
+        <v>0.3641863028382526</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1176713886878296</v>
+        <v>0.3679368009853795</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1188708509978285</v>
+        <v>0.3716872991325064</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1200703133078275</v>
+        <v>0.3754377972796333</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1212697756178265</v>
+        <v>0.3791882954267602</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1224692379278255</v>
+        <v>0.382938793573887</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1236687002378244</v>
+        <v>0.3866892917210139</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1248681625478234</v>
+        <v>0.3904397898681408</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1260676248578223</v>
+        <v>0.3941902880152677</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1272670871678213</v>
+        <v>0.3979407861623947</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1284665494778203</v>
+        <v>0.4016912843095216</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1296660117878193</v>
+        <v>0.4054417824566484</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1068762278978389</v>
+        <v>0.3341823176612375</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1080756902078379</v>
+        <v>0.3379328158083644</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1092751525178368</v>
+        <v>0.3416833139554912</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1104746148278358</v>
+        <v>0.3454338121026181</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1116740771378347</v>
+        <v>0.349184310249745</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1128735394478337</v>
+        <v>0.3529348083968719</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1140730017578327</v>
+        <v>0.3566853065439988</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1152724640678317</v>
+        <v>0.3604358046911257</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1164719263778306</v>
+        <v>0.3641863028382526</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1176713886878296</v>
+        <v>0.3679368009853795</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1188708509978285</v>
+        <v>0.3716872991325064</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1200703133078275</v>
+        <v>0.3754377972796333</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1212697756178265</v>
+        <v>0.3791882954267602</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1224692379278255</v>
+        <v>0.382938793573887</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1236687002378244</v>
+        <v>0.3866892917210139</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1248681625478234</v>
+        <v>0.3904397898681408</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1260676248578223</v>
+        <v>0.3941902880152677</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1272670871678213</v>
+        <v>0.3979407861623947</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1284665494778203</v>
+        <v>0.4016912843095216</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1296660117878193</v>
+        <v>0.4054417824566484</v>
       </c>
     </row>
   </sheetData>
